--- a/src/main/resources/testdata.xlsx
+++ b/src/main/resources/testdata.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{8F95CAF0-9D55-4C39-85F9-912ECCE0EB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/448a155a15185903/Documents/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{9CD72E36-18F3-4E72-97A9-B90BFD7B2796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71DB7537-64D0-451B-BF6A-4B769C780B56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1AE9CBB-15FA-476B-941D-7FD16D8340D2}"/>
   </bookViews>
@@ -11,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -21,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -95,7 +99,34 @@
     <t>2005</t>
   </si>
   <si>
-    <t>sravya22@gmail.com</t>
+    <t>sravya33@gmail.com</t>
+  </si>
+  <si>
+    <t>Kavya</t>
+  </si>
+  <si>
+    <t>Basu</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>kavya18@gmail.com</t>
+  </si>
+  <si>
+    <t>street3</t>
+  </si>
+  <si>
+    <t>KLU</t>
+  </si>
+  <si>
+    <t>vijayawada</t>
   </si>
 </sst>
 </file>
@@ -579,11 +610,48 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>234567</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3">
+        <v>522035</v>
+      </c>
+      <c r="N3">
+        <v>8687239686</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
@@ -595,6 +663,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{7DEE28B3-4A20-4707-8624-CE66F305F53C}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{BEB09491-BF84-4FFC-9465-8FEDF4EE8E57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
